--- a/rules/CORE-000761/negative/01/data/unit-test-coreid-CG0289-negative.xlsx
+++ b/rules/CORE-000761/negative/01/data/unit-test-coreid-CG0289-negative.xlsx
@@ -44,7 +44,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +126,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="6" max="6"/>
@@ -653,7 +659,7 @@
           <t>TSVCDVER</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2021-03-27</t>
         </is>
@@ -661,7 +667,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -673,17 +679,43 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D4" t="n">
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TSVCDREF</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CDISC CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TSVCDVER</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2025-13-45</t>
         </is>
@@ -1448,12 +1480,12 @@
           <t>C49488</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>CDISC CT</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>2025-13-45</t>
         </is>
